--- a/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 17,39</t>
+          <t>-0,42; 18,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 24,68</t>
+          <t>9,29; 24,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 20,32</t>
+          <t>4,41; 19,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 13,64</t>
+          <t>-1,96; 14,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 44,41</t>
+          <t>-1,2; 46,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 43,49</t>
+          <t>14,17; 43,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 39,76</t>
+          <t>7,26; 37,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 23,17</t>
+          <t>-3,11; 24,14</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,35; 24,87</t>
+          <t>11,94; 25,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,76; 23,12</t>
+          <t>11,1; 23,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 19,88</t>
+          <t>7,69; 19,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 11,78</t>
+          <t>-1,89; 11,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,12; 57,56</t>
+          <t>23,82; 57,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 47,06</t>
+          <t>19,59; 48,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,39; 36,38</t>
+          <t>12,66; 36,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 32,67</t>
+          <t>-4,01; 32,27</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 30,91</t>
+          <t>15,9; 30,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 16,63</t>
+          <t>1,51; 16,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 16,11</t>
+          <t>1,99; 16,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 9,81</t>
+          <t>-4,79; 9,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,09; 77,14</t>
+          <t>31,95; 76,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 30,45</t>
+          <t>2,42; 29,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 33,55</t>
+          <t>3,41; 34,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 21,86</t>
+          <t>-8,87; 21,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 24,88</t>
+          <t>10,83; 24,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 19,31</t>
+          <t>5,27; 18,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 19,72</t>
+          <t>5,21; 19,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 8,08</t>
+          <t>-20,81; 9,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,9; 51,71</t>
+          <t>19,09; 51,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 36,2</t>
+          <t>8,3; 34,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 36,38</t>
+          <t>8,8; 35,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,76; 19,19</t>
+          <t>-43,81; 21,69</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 25,59</t>
+          <t>7,04; 25,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,3; 34,35</t>
+          <t>17,21; 34,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 20,92</t>
+          <t>2,2; 20,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 7,26</t>
+          <t>-6,67; 8,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 58,6</t>
+          <t>12,64; 56,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,63; 69,3</t>
+          <t>27,62; 69,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 43,86</t>
+          <t>3,87; 43,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 66,88</t>
+          <t>-41,73; 77,01</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 22,44</t>
+          <t>5,79; 22,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,94; 22,41</t>
+          <t>7,14; 22,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 21,1</t>
+          <t>4,25; 21,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 7,7</t>
+          <t>-7,49; 7,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,35; 49,28</t>
+          <t>10,6; 50,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 39,29</t>
+          <t>10,52; 39,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,74; 48,01</t>
+          <t>7,72; 49,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 14,95</t>
+          <t>-12,48; 13,34</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,65; 22,06</t>
+          <t>10,39; 21,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 16,9</t>
+          <t>5,45; 16,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 17,65</t>
+          <t>6,08; 17,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 42,53</t>
+          <t>3,96; 45,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,73; 52,3</t>
+          <t>20,95; 49,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,6; 30,88</t>
+          <t>9,22; 29,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,68; 42,75</t>
+          <t>12,75; 42,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,3; 141,87</t>
+          <t>11,21; 151,83</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,11; 17,2</t>
+          <t>7,27; 16,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,5; 16,1</t>
+          <t>6,01; 16,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,74</t>
+          <t>4,72; 14,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,03; 35,69</t>
+          <t>10,21; 33,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,34; 35,48</t>
+          <t>13,54; 33,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,05; 36,19</t>
+          <t>11,88; 37,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,48; 30,46</t>
+          <t>8,47; 30,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,86; 300,66</t>
+          <t>29,48; 295,88</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,35; 18,09</t>
+          <t>13,46; 18,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,8</t>
+          <t>11,37; 16,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,72</t>
+          <t>9,32; 14,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,84; 21,15</t>
+          <t>3,8; 22,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,26; 38,54</t>
+          <t>27,03; 38,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,91; 29,0</t>
+          <t>19,95; 29,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,13; 26,82</t>
+          <t>17,34; 27,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,4; 65,91</t>
+          <t>9,46; 65,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,96</t>
+          <t>6,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 18,28</t>
+          <t>-0,14; 17,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 24,54</t>
+          <t>9,29; 24,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 19,48</t>
+          <t>3,99; 19,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 14,18</t>
+          <t>-1,14; 13,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 46,94</t>
+          <t>-0,28; 45,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,17; 43,92</t>
+          <t>14,16; 43,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 37,66</t>
+          <t>6,52; 38,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 24,14</t>
+          <t>-1,67; 25,17</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>5,38</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 25,01</t>
+          <t>12,26; 24,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 23,56</t>
+          <t>11,56; 23,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 19,7</t>
+          <t>7,32; 19,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 11,57</t>
+          <t>-1,11; 11,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,82; 57,84</t>
+          <t>24,29; 56,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 48,32</t>
+          <t>20,95; 48,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 36,55</t>
+          <t>12,41; 37,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 32,27</t>
+          <t>-2,42; 32,99</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,9; 30,66</t>
+          <t>15,51; 30,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 16,76</t>
+          <t>1,51; 16,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 16,62</t>
+          <t>1,5; 16,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 9,5</t>
+          <t>-4,42; 10,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,95; 76,66</t>
+          <t>32,07; 77,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 29,79</t>
+          <t>1,98; 29,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 34,2</t>
+          <t>2,85; 35,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 21,6</t>
+          <t>-8,52; 23,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-8,95%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 24,29</t>
+          <t>10,46; 24,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 18,82</t>
+          <t>4,66; 18,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 19,22</t>
+          <t>6,14; 20,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,81; 9,11</t>
+          <t>-1,54; 15,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,09; 51,15</t>
+          <t>18,82; 51,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 34,24</t>
+          <t>7,52; 34,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 35,53</t>
+          <t>9,86; 37,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 21,69</t>
+          <t>-2,34; 40,93</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>5,72</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 25,34</t>
+          <t>6,68; 25,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 34,64</t>
+          <t>17,64; 35,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 20,55</t>
+          <t>1,4; 20,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 8,05</t>
+          <t>0,3; 10,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 56,85</t>
+          <t>11,78; 59,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,62; 69,06</t>
+          <t>28,56; 71,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 43,18</t>
+          <t>2,39; 43,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 77,01</t>
+          <t>0,71; 107,65</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-0,05%</t>
+          <t>-0,94%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 22,52</t>
+          <t>4,67; 22,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 22,91</t>
+          <t>7,66; 22,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 21,35</t>
+          <t>2,56; 20,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 7,12</t>
+          <t>-7,91; 7,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 50,11</t>
+          <t>8,87; 48,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,52; 39,75</t>
+          <t>11,27; 39,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,72; 49,59</t>
+          <t>7,01; 48,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 13,34</t>
+          <t>-12,96; 12,95</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,7</t>
+          <t>7,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 21,33</t>
+          <t>9,86; 20,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 16,22</t>
+          <t>5,3; 16,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 17,56</t>
+          <t>6,14; 17,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,96; 45,58</t>
+          <t>1,89; 12,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,95; 49,31</t>
+          <t>20,25; 47,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,22; 29,64</t>
+          <t>8,97; 29,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,75; 42,49</t>
+          <t>13,37; 42,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,21; 151,83</t>
+          <t>5,4; 41,16</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,45</t>
+          <t>12,12</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 16,63</t>
+          <t>6,63; 16,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 16,43</t>
+          <t>6,58; 16,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 14,68</t>
+          <t>4,93; 15,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,21; 33,82</t>
+          <t>7,75; 16,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,54; 33,96</t>
+          <t>12,09; 34,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,88; 37,24</t>
+          <t>13,13; 36,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,47; 30,0</t>
+          <t>9,22; 31,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>29,48; 295,88</t>
+          <t>21,66; 55,45</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>6,69</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13,46; 18,0</t>
+          <t>13,23; 18,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,37; 16,16</t>
+          <t>11,17; 16,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,32; 14,0</t>
+          <t>9,02; 13,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,8; 22,19</t>
+          <t>4,48; 9,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,03; 38,58</t>
+          <t>26,86; 38,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,95; 29,61</t>
+          <t>19,68; 29,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,34; 27,43</t>
+          <t>17,1; 27,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,46; 65,97</t>
+          <t>10,97; 24,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
